--- a/output/pdf_financials_xlsx/SVB.xlsx
+++ b/output/pdf_financials_xlsx/SVB.xlsx
@@ -486,15 +486,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -520,15 +516,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.571064</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.446853</v>
       </c>
     </row>
     <row r="8">
@@ -537,15 +529,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -554,15 +542,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -571,15 +555,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.571064</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.446853</v>
       </c>
     </row>
     <row r="11">
@@ -588,15 +568,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-3.002024</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-4.360968</v>
       </c>
     </row>
     <row r="12">
@@ -605,15 +581,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -623,12 +595,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.002329</v>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -637,15 +607,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -654,15 +620,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.513924</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.427708</v>
       </c>
     </row>
     <row r="16">
@@ -731,15 +693,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-3.519666</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-3.938569</v>
       </c>
     </row>
     <row r="21">
@@ -748,15 +706,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -765,15 +719,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -782,15 +732,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-3.519666</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-3.938569</v>
       </c>
     </row>
     <row r="24">
@@ -850,15 +796,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-3.515948</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-3.93326</v>
       </c>
     </row>
     <row r="28">
@@ -867,15 +809,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -884,15 +822,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-3.515948</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-3.93326</v>
       </c>
     </row>
     <row r="30">
@@ -968,15 +902,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -985,15 +915,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>3.025839</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1.431634</v>
       </c>
     </row>
     <row r="37">
@@ -1002,15 +928,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1019,15 +941,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1036,15 +954,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1066,15 +980,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.012045</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.008543</v>
       </c>
     </row>
     <row r="42">
@@ -1083,15 +993,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1100,15 +1006,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1117,15 +1019,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1134,15 +1032,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1151,15 +1045,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1168,15 +1058,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1185,15 +1071,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.412433</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.461344</v>
       </c>
     </row>
     <row r="49">
@@ -1215,15 +1097,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1232,15 +1110,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1249,15 +1123,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1266,15 +1136,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1283,15 +1149,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1317,15 +1179,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1334,15 +1192,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1351,15 +1205,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1368,15 +1218,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1398,15 +1244,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>5.221413</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>5.24634</v>
       </c>
     </row>
     <row r="62">
@@ -1415,15 +1257,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>7.279444</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>7.304371</v>
       </c>
     </row>
     <row r="63">
@@ -1458,15 +1296,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1475,15 +1309,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1492,15 +1322,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1509,15 +1335,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.253327</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.328943</v>
       </c>
     </row>
     <row r="69">
@@ -1526,15 +1348,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1543,15 +1361,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1560,15 +1374,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1577,15 +1387,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1594,15 +1400,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1611,15 +1413,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1628,15 +1426,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.874766</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.312074</v>
       </c>
     </row>
     <row r="76">
@@ -1658,15 +1452,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1675,15 +1465,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1692,15 +1478,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1726,15 +1508,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1743,15 +1521,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1760,15 +1534,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1777,15 +1547,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1794,15 +1560,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1811,15 +1573,11 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1828,15 +1586,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>1.128093</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.6410169999999999</v>
       </c>
     </row>
     <row r="88">
@@ -1845,15 +1599,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1862,15 +1612,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1892,15 +1638,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1922,15 +1664,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1952,15 +1690,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1969,15 +1703,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>9.601668</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>8.564875000000001</v>
       </c>
     </row>
     <row r="97">
@@ -2006,15 +1736,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-3.519666</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-3.938569</v>
       </c>
     </row>
     <row r="100">
@@ -2023,15 +1749,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2040,15 +1762,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.006865</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.003641</v>
       </c>
     </row>
     <row r="102">
@@ -2057,15 +1775,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2074,15 +1788,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.121499</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.03109</v>
       </c>
     </row>
     <row r="104">
@@ -2092,12 +1802,10 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>0.050653</v>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.172137</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.071476</v>
       </c>
     </row>
     <row r="105">
@@ -2106,15 +1814,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2123,15 +1827,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.043773</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.106207</v>
       </c>
     </row>
     <row r="107">
@@ -2140,15 +1840,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2157,15 +1853,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2174,15 +1866,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2191,15 +1879,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2208,15 +1892,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2225,15 +1905,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2242,15 +1918,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2259,15 +1931,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2276,15 +1944,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2293,15 +1957,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2310,15 +1970,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2327,15 +1983,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2357,15 +2009,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2374,15 +2022,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2391,15 +2035,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2408,15 +2048,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2425,15 +2061,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2442,15 +2074,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2459,15 +2087,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2493,15 +2117,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2536,15 +2156,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2579,15 +2195,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2596,15 +2208,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-2.647377</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-4.209129</v>
       </c>
     </row>
   </sheetData>
@@ -3257,7 +2865,11 @@
           <t>Net loss $</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-3.519666</v>
       </c>
@@ -3473,7 +3085,11 @@
           <t>Other receivables</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.006865</v>
       </c>
@@ -3497,7 +3113,11 @@
           <t>Prepaid expenses and deposits</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.121499</v>
       </c>
@@ -3521,7 +3141,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.121484</v>
       </c>
@@ -4629,7 +4253,11 @@
           <t>Office and administrative</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
         <v>0.571064</v>
       </c>
@@ -4753,7 +4381,11 @@
           <t>LOSS FROM OPERATIONS</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>-3.002024</v>
       </c>
@@ -4805,11 +4437,7 @@
           <t>Interest and finance costs</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
         <v>-0.002329</v>
       </c>
@@ -4933,7 +4561,11 @@
           <t>TOTAL OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>-0.513924</v>
       </c>
@@ -5013,7 +4645,11 @@
           <t>NET AND COMPREHENSIVE LOSS $</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>-3.519666</v>
       </c>

--- a/output/pdf_financials_xlsx/SVB.xlsx
+++ b/output/pdf_financials_xlsx/SVB.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SVB.xlsx
+++ b/output/pdf_financials_xlsx/SVB.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.003718</v>
+        <v>-0.003718</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.005309</v>
+        <v>-0.005309</v>
       </c>
     </row>
     <row r="18">
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2280,24 +2280,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CURRENT ASSETS</t>
+          <t>Vancouver, Canada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents $</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" s="5" t="n">
-        <v>3.025839</v>
+        <v>0.00202</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1.431634</v>
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2313,15 +2309,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Value-added tax receivable, net of allowance for uncollectible taxes of $327,624 and $98,414, respectively (Note 4)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Cash and cash equivalents $</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n">
-        <v>0.17502</v>
+        <v>3.025839</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.255847</v>
+        <v>1.431634</v>
       </c>
     </row>
     <row r="4">
@@ -2337,15 +2337,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Income tax receivables</t>
+          <t>Value-added tax receivable, net of allowance for uncollectible taxes of $327,624 and $98,414, respectively (Note 4)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="5" t="n">
-        <v>0.00016</v>
+        <v>0.17502</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.000784</v>
+        <v>0.255847</v>
       </c>
     </row>
     <row r="5">
@@ -2361,19 +2361,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other receivables</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OtherReceivables</t>
-        </is>
-      </c>
+          <t>Income tax receivables</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="5" t="n">
-        <v>0.012045</v>
+        <v>0.00016</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.008543</v>
+        <v>0.000784</v>
       </c>
     </row>
     <row r="6">
@@ -2389,19 +2385,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
+          <t>OtherReceivables</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.237253</v>
+        <v>0.012045</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.204713</v>
+        <v>0.008543</v>
       </c>
     </row>
     <row r="7">
@@ -2417,19 +2413,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Total Current Assets</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.450317</v>
+        <v>0.237253</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.901521</v>
+        <v>0.204713</v>
       </c>
     </row>
     <row r="8">
@@ -2445,15 +2441,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Office and mining equipment, net (Note 5)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
-        <v>0.201486</v>
+        <v>3.450317</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.226413</v>
+        <v>1.901521</v>
       </c>
     </row>
     <row r="9">
@@ -2469,15 +2469,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Property concessions (Note 6)</t>
+          <t>Office and mining equipment, net (Note 5)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="5" t="n">
-        <v>5.019927</v>
+        <v>0.201486</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>5.019927</v>
+        <v>0.226413</v>
       </c>
     </row>
     <row r="10">
@@ -2493,19 +2493,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Goodwill (Note 7)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
+          <t>Property concessions (Note 6)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="5" t="n">
-        <v>2.058031</v>
+        <v>5.019927</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2.058031</v>
+        <v>5.019927</v>
       </c>
     </row>
     <row r="11">
@@ -2521,19 +2517,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOTAL ASSETS $</t>
+          <t>Goodwill (Note 7)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>10.729761</v>
+        <v>2.058031</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>9.205892</v>
+        <v>2.058031</v>
       </c>
     </row>
     <row r="12">
@@ -2544,24 +2540,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CURRENT LIABILITIES</t>
+          <t>CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accounts payable $</t>
+          <t>TOTAL ASSETS $</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AccountsPayable</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.253327</v>
+        <v>10.729761</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.328943</v>
+        <v>9.205892</v>
       </c>
     </row>
     <row r="13">
@@ -2577,15 +2573,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Accrued liabilities and expenses</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Accounts payable $</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
-        <v>0.43945</v>
+        <v>0.253327</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.305446</v>
+        <v>0.328943</v>
       </c>
     </row>
     <row r="14">
@@ -2601,19 +2601,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Income tax payable</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>IncomeTaxPayable</t>
-        </is>
-      </c>
+          <t>Accrued liabilities and expenses</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" s="5" t="n">
-        <v>0.0047</v>
+        <v>0.43945</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.001825</v>
+        <v>0.305446</v>
       </c>
     </row>
     <row r="15">
@@ -2629,15 +2625,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stock option liability (Note 9)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Income tax payable</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
-        <v>0.025116</v>
+        <v>0.0047</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.004803</v>
+        <v>0.001825</v>
       </c>
     </row>
     <row r="16">
@@ -2653,17 +2653,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Warrant derivative liability (Note 10)</t>
+          <t>Stock option liability (Note 9)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="5" t="n">
-        <v>0.4055</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025116</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.004803</v>
       </c>
     </row>
     <row r="17">
@@ -2679,19 +2677,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
+          <t>Warrant derivative liability (Note 10)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>1.128093</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.6410169999999999</v>
+        <v>0.4055</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -2702,20 +2698,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Common stock, $0.01 par value; 300,000,000 shares authorized,</t>
+          <t>CURRENT LIABILITIES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>236,328,214 and 234,868,214 shares issued and outstanding, respectively</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>2.348682</v>
+        <v>1.128093</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>2.363282</v>
+        <v>0.6410169999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2731,19 +2731,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional paid-in capital</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>236,328,214 and 234,868,214 shares issued and outstanding, respectively</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" s="5" t="n">
-        <v>133.015768</v>
+        <v>2.348682</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>135.902944</v>
+        <v>2.363282</v>
       </c>
     </row>
     <row r="20">
@@ -2759,19 +2755,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Additional paid-in capital</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-125.85503</v>
+        <v>133.015768</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-129.793599</v>
+        <v>135.902944</v>
       </c>
     </row>
     <row r="21">
@@ -2787,15 +2783,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>0.092248</v>
+        <v>-125.85503</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.092248</v>
+        <v>-129.793599</v>
       </c>
     </row>
     <row r="22">
@@ -2811,19 +2811,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Total Stockholders’ Equity</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
-        <v>9.601668</v>
+        <v>0.092248</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>8.564875000000001</v>
+        <v>0.092248</v>
       </c>
     </row>
     <row r="23">
@@ -2839,47 +2835,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND STOCKHOLDERS’ EQUITY $</t>
+          <t>Total Stockholders’ Equity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10.729761</v>
+        <v>9.601668</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>9.205892</v>
+        <v>8.564875000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Common stock, $0.01 par value; 300,000,000 shares authorized,</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>TOTAL LIABILITIES AND STOCKHOLDERS’ EQUITY $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-3.519666</v>
+        <v>10.729761</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-3.938569</v>
+        <v>9.205892</v>
       </c>
     </row>
     <row r="25">
@@ -2895,15 +2891,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Depreciation, asset and property concessions’ impairment</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
-        <v>0.027105</v>
+        <v>-3.519666</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.044119</v>
+        <v>-3.938569</v>
       </c>
     </row>
     <row r="26">
@@ -2919,15 +2919,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Provision for uncollectible value-added taxes</t>
+          <t>Depreciation, asset and property concessions’ impairment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.037457</v>
+        <v>0.027105</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.22213</v>
+        <v>0.044119</v>
       </c>
     </row>
     <row r="27">
@@ -2943,15 +2943,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foreign currency transaction loss (gain)</t>
+          <t>Provision for uncollectible value-added taxes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="5" t="n">
-        <v>-0.004132</v>
+        <v>0.037457</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.000145</v>
+        <v>0.22213</v>
       </c>
     </row>
     <row r="28">
@@ -2967,15 +2967,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant derivative liability (Note 10)</t>
+          <t>Foreign currency transaction loss (gain)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.510968</v>
+        <v>-0.004132</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.393374</v>
+        <v>0.000145</v>
       </c>
     </row>
     <row r="29">
@@ -2991,15 +2991,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Change in fair value of stock option liability (Note 9)</t>
+          <t>Change in fair value of warrant derivative liability (Note 10)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
-        <v>-0.008189</v>
+        <v>0.510968</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.021105</v>
+        <v>-0.393374</v>
       </c>
     </row>
     <row r="30">
@@ -3015,15 +3015,15 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stock options issued for compensation (Note 9)</t>
+          <t>Change in fair value of stock option liability (Note 9)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
-        <v>0.245629</v>
+        <v>-0.008189</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.206756</v>
+        <v>-0.021105</v>
       </c>
     </row>
     <row r="31">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Value-added tax receivable</t>
+          <t>Stock options issued for compensation (Note 9)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>-0.064635</v>
+        <v>0.245629</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-0.288673</v>
+        <v>0.206756</v>
       </c>
     </row>
     <row r="32">
@@ -3063,15 +3063,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Income tax receivables</t>
+          <t>Value-added tax receivable</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>-0.00017</v>
+        <v>-0.064635</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.000604</v>
+        <v>-0.288673</v>
       </c>
     </row>
     <row r="33">
@@ -3087,19 +3087,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Other receivables</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Income tax receivables</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>-0.006865</v>
+        <v>-0.00017</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.003641</v>
+        <v>-0.000604</v>
       </c>
     </row>
     <row r="34">
@@ -3115,19 +3111,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.121499</v>
+        <v>-0.006865</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.03109</v>
+        <v>0.003641</v>
       </c>
     </row>
     <row r="35">
@@ -3143,19 +3139,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
+          <t>Prepaid expenses and deposits</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.121484</v>
+        <v>-0.121499</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.071476</v>
+        <v>0.03109</v>
       </c>
     </row>
     <row r="36">
@@ -3171,15 +3167,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Accrued liabilities and expenses</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.135216</v>
+        <v>0.121484</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.143286</v>
+        <v>0.071476</v>
       </c>
     </row>
     <row r="37">
@@ -3195,15 +3195,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Income tax payable</t>
+          <t>Accrued liabilities and expenses</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>0.135216</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.002875</v>
+        <v>-0.143286</v>
       </c>
     </row>
     <row r="38">
@@ -3219,19 +3219,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Income tax payable</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>-2.647377</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-4.209129</v>
+        <v>-0.002875</v>
       </c>
     </row>
     <row r="39">
@@ -3242,20 +3238,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Acquisition of property concessions</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>-0.015541</v>
+        <v>-2.647377</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-0.011821</v>
+        <v>-4.209129</v>
       </c>
     </row>
     <row r="40">
@@ -3271,15 +3271,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Acquisition of property concessions</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>-0.019836</v>
+        <v>-0.015541</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.057224</v>
+        <v>-0.011821</v>
       </c>
     </row>
     <row r="41">
@@ -3295,19 +3295,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Purchase of equipment</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>-0.035377</v>
+        <v>-0.019836</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.069045</v>
+        <v>-0.057224</v>
       </c>
     </row>
     <row r="42">
@@ -3318,20 +3314,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Property concessions funding (Note 3)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>0.922783</v>
+        <v>-0.035377</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>2.54081</v>
+        <v>-0.069045</v>
       </c>
     </row>
     <row r="43">
@@ -3347,15 +3347,15 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants, net of costs (Note 8)</t>
+          <t>Property concessions funding (Note 3)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.633908</v>
+        <v>0.922783</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.142876</v>
+        <v>2.54081</v>
       </c>
     </row>
     <row r="44">
@@ -3371,17 +3371,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common stock, net of offering costs (Note 8)</t>
+          <t>Proceeds from exercise of warrants, net of costs (Note 8)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>3.469657</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.633908</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.142876</v>
       </c>
     </row>
     <row r="45">
@@ -3397,19 +3395,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of common stock, net of offering costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>5.026348</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>2.683686</v>
+        <v>3.469657</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3425,15 +3421,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Effect of exchange rates on cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>0.000469</v>
+        <v>5.026348</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.000283</v>
+        <v>2.683686</v>
       </c>
     </row>
     <row r="47">
@@ -3449,19 +3449,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Net (decrease) increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Effect of exchange rates on cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>2.344063</v>
+        <v>0.000469</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-1.594205</v>
+        <v>0.000283</v>
       </c>
     </row>
     <row r="48">
@@ -3477,19 +3473,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents beginning of year</t>
+          <t>Net (decrease) increase in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.681776</v>
+        <v>2.344063</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>3.025839</v>
+        <v>-1.594205</v>
       </c>
     </row>
     <row r="49">
@@ -3505,19 +3501,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents end of year $</t>
+          <t>Cash and cash equivalents beginning of year</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
+        <v>0.681776</v>
+      </c>
+      <c r="F49" s="5" t="n">
         <v>3.025839</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1.431634</v>
       </c>
     </row>
     <row r="50">
@@ -3528,20 +3524,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SUPPLEMENTAL CASH FLOW DISCLOSURES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Income taxes paid $</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Cash and cash equivalents end of year $</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.004599</v>
+        <v>3.025839</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.00808</v>
+        <v>1.431634</v>
       </c>
     </row>
     <row r="51">
@@ -3557,17 +3557,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Interest paid $</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Income taxes paid $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
-        <v>0.002329</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004599</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.00808</v>
       </c>
     </row>
     <row r="52">
@@ -3578,17 +3580,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NON-CASH INVESTING AND FINANCING ACTIVITIES</t>
+          <t>SUPPLEMENTAL CASH FLOW DISCLOSURES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warrants issued for financing fees (Note 8) $</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Interest paid $</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
-        <v>0.026165</v>
+        <v>0.002329</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3609,16 +3615,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Offering costs included in accounts payable and accrued liabilities $</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Warrants issued for financing fees (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.050653</v>
+        <v>0.026165</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3634,20 +3636,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capital Income</t>
+          <t>NON-CASH INVESTING AND FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Balance, November 1, 2017 199,259,967 $ 1,992,599 $127,679,664 $ (122,335,364) $</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Offering costs included in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>7.429147</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.092248</v>
+        <v>0.050653</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3658,22 +3666,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Issuance of common stock as follows</t>
+          <t>Capital                           Income</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>- for cash at a price of $0.13 per share with attached warrants, less offering costs of $343,816 (Note 8) 29,141,872 291,419 3,153,208 —</t>
+          <t>Balance, November 1, 2017 199,259,967 $ 1,992,599 $ 127,679,664 $ (122,335,364) $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>3.444627</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.429147</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.092248</v>
       </c>
     </row>
     <row r="56">
@@ -3689,12 +3695,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>- exercise of warrants at a price of $CDN 0.13 per share, less costs of $795 (Note 8) 5,565,000 55,650 508,689 —</t>
+          <t>- for cash at a price of $0.13 per share with attached warrants, less offering costs of $343,816 (Note 8) 29,141,872 291,419 3,153,208 —</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>0.564339</v>
+        <v>3.444627</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3715,12 +3721,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>- exercise of agent warrants at a price of $CDN 0.10 per share, less costs of $333 (Note 8) 901,375 9,014 60,556 —</t>
+          <t>- exercise of warrants at a price of $CDN 0.13 per share, less costs of $795 (Note 8) 5,565,000 55,650 508,689 —</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.06957000000000001</v>
+        <v>0.564339</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3741,12 +3747,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Earn-In Option Agreement (Note 3) — — 922,783 —</t>
+          <t>- exercise of agent warrants at a price of $CDN 0.10 per share, less costs of $333 (Note 8) 901,375 9,014 60,556 —</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.922783</v>
+        <v>0.06957000000000001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3762,17 +3768,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Stock-based compensation for options issued to directors, officers,</t>
+          <t>Issuance of common stock as follows</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stock-based compensation for options issued to directors, officers, employees and consultants — — 245,629 —</t>
+          <t>Earn-In Option Agreement (Note 3) — — 922,783 —</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.245629</v>
+        <v>0.922783</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3793,12 +3799,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$0.13 per share private placement (Notes 8 and 10) — — 26,165 —</t>
+          <t>Stock-based compensation for options issued to directors, officers, employees and consultants — — 245,629 —</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.026165</v>
+        <v>0.245629</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3819,12 +3825,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Reclassification of consultants’ stock options to liability (Note 9) — — (28,111) —</t>
+          <t>$0.13 per share private placement (Notes 8 and 10) — — 26,165 —</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>-0.028111</v>
+        <v>0.026165</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3840,17 +3846,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Reclassification to additional paid-in capital upon exercise of</t>
+          <t>Stock-based compensation for options issued to directors, officers,</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.13 (Note 10) — — 385,738 —</t>
+          <t>Reclassification of consultants’ stock options to liability (Note 9) — — (28,111) —</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.385738</v>
+        <v>-0.028111</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3871,12 +3877,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.10 (Note 10) — — 61,447 —</t>
+          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.13 (Note 10) — — 385,738 —</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.061447</v>
+        <v>0.385738</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3897,12 +3903,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Net loss for the year ended October 31, 2018 — — — (3,519,666)</t>
+          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.10 (Note 10) — — 61,447 —</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>-3.519666</v>
+        <v>0.061447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3923,15 +3929,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Balance, October 31, 2018 234,868,214 $ 2,348,682 $133,015,768 $ (125,855,030) $</t>
+          <t>Net loss for the year ended October 31, 2018 — — — (3,519,666)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>9.601668</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0.092248</v>
+        <v>-3.519666</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -3942,22 +3950,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Issuance of common stock as follows</t>
+          <t>Reclassification to additional paid-in capital upon exercise of</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>$210 (Note 8) 1,460,000 14,600 128,276 —</t>
+          <t>Balance, October 31, 2018 234,868,214 $ 2,348,682 $ 133,015,768 $ (125,855,030) $</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>0.142876</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.601668</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.092248</v>
       </c>
     </row>
     <row r="67">
@@ -3973,12 +3979,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Earn-In Option Agreement (Note 3) — — 2,540,810 —</t>
+          <t>$210 (Note 8) 1,460,000 14,600 128,276 —</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>2.54081</v>
+        <v>0.142876</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3994,17 +4000,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Reclassification to additional paid-in capital upon exercise of</t>
+          <t>Issuance of common stock as follows</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.13 (Note 10) — — 12,126 —</t>
+          <t>Earn-In Option Agreement (Note 3) — — 2,540,810 —</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>0.012126</v>
+        <v>2.54081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4025,12 +4031,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reclassification of consultants’ stock options to liability (Note 9) — — (792) —</t>
+          <t>Reclassification to additional paid-in capital upon exercise of warrants at price of $CDN 0.13 (Note 10) — — 12,126 —</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>-0.000792</v>
+        <v>0.012126</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4046,17 +4052,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stock-based compensation for options issued to directors, officers,</t>
+          <t>Reclassification to additional paid-in capital upon exercise of</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Stock-based compensation for options issued to directors, officers, employees and consultants — — 206,756 —</t>
+          <t>Reclassification of consultants’ stock options to liability (Note 9) — — (792) —</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>0.206756</v>
+        <v>-0.000792</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4077,12 +4083,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net loss for the year ended October 31, 2019 — — — (3,938,569)</t>
+          <t>Stock-based compensation for options issued to directors, officers, employees and consultants — — 206,756 —</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>-3.938569</v>
+        <v>0.206756</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4103,47 +4109,41 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, October 31, 2019 236,328,214 $ 2,363,282 $135,902,944 $ (129,793,599) $</t>
+          <t>Net loss for the year ended October 31, 2019 — — — (3,938,569)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>8.564875000000001</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.092248</v>
+        <v>-3.938569</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(AN EXPLORATION STAGE COMPANY)</t>
+          <t>Stock-based compensation for options issued to directors, officers,</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REVENUES $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, October 31, 2019 236,328,214 $ 2,363,282 $ 135,902,944 $ (129,793,599) $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>8.564875000000001</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.092248</v>
       </c>
     </row>
     <row r="74">
@@ -4154,20 +4154,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXPLORATION AND PROPERTY HOLDING COSTS</t>
+          <t>(AN EXPLORATION STAGE COMPANY)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Exploration and property holding costs</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>1.213519</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>2.508602</v>
+          <t>REVENUES $</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4183,15 +4191,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Depreciation, asset and property concessions’ impairment (Notes 5 and 6)</t>
+          <t>Exploration and property holding costs</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0.027105</v>
+        <v>1.213519</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.044119</v>
+        <v>2.508602</v>
       </c>
     </row>
     <row r="76">
@@ -4207,15 +4215,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TOTAL EXPLORATION AND PROPERTY HOLDING COSTS</t>
+          <t>Depreciation, asset and property concessions’ impairment (Notes 5 and 6)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>1.240624</v>
+        <v>0.027105</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>2.552721</v>
+        <v>0.044119</v>
       </c>
     </row>
     <row r="77">
@@ -4226,20 +4234,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
+          <t>EXPLORATION AND PROPERTY HOLDING COSTS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>TOTAL EXPLORATION AND PROPERTY HOLDING COSTS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>0.70156</v>
+        <v>1.240624</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.692242</v>
+        <v>2.552721</v>
       </c>
     </row>
     <row r="78">
@@ -4255,19 +4263,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Personnel</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>0.571064</v>
+        <v>0.70156</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.446853</v>
+        <v>0.692242</v>
       </c>
     </row>
     <row r="79">
@@ -4283,15 +4287,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Professional services</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
-        <v>0.224846</v>
+        <v>0.571064</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.245949</v>
+        <v>0.446853</v>
       </c>
     </row>
     <row r="80">
@@ -4307,15 +4315,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Directors’ fees</t>
+          <t>Professional services</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>0.226473</v>
+        <v>0.224846</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.201073</v>
+        <v>0.245949</v>
       </c>
     </row>
     <row r="81">
@@ -4331,15 +4339,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Provision for uncollectible value-added taxes (Note 4)</t>
+          <t>Directors’ fees</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>0.037457</v>
+        <v>0.226473</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.22213</v>
+        <v>0.201073</v>
       </c>
     </row>
     <row r="82">
@@ -4355,19 +4363,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TOTAL GENERAL AND ADMINISTRATIVE EXPENSES</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Provision for uncollectible value-added taxes (Note 4)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
-        <v>1.7614</v>
+        <v>0.037457</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>1.808247</v>
+        <v>0.22213</v>
       </c>
     </row>
     <row r="83">
@@ -4383,19 +4387,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS</t>
+          <t>TOTAL GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>-3.002024</v>
+        <v>1.7614</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-4.360968</v>
+        <v>1.808247</v>
       </c>
     </row>
     <row r="84">
@@ -4406,24 +4410,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OTHER INCOME (EXPENSES)</t>
+          <t>GENERAL AND ADMINISTRATIVE EXPENSES</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>LOSS FROM OPERATIONS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.004065</v>
+        <v>-3.002024</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.028443</v>
+        <v>-4.360968</v>
       </c>
     </row>
     <row r="85">
@@ -4439,17 +4443,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Interest and finance costs</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
-        <v>-0.002329</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004065</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.028443</v>
       </c>
     </row>
     <row r="86">
@@ -4465,15 +4471,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Foreign currency transaction loss</t>
+          <t>Interest and finance costs</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>-0.013106</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.015214</v>
+        <v>-0.002329</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -4489,15 +4497,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Change in fair value of stock option liability (Note 9)</t>
+          <t>Foreign currency transaction loss</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" s="5" t="n">
-        <v>0.008189</v>
+        <v>-0.013106</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.021105</v>
+        <v>-0.015214</v>
       </c>
     </row>
     <row r="88">
@@ -4513,15 +4521,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Change in fair value of warrant derivative liability (Note 10)</t>
+          <t>Change in fair value of stock option liability (Note 9)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" s="5" t="n">
-        <v>-0.510968</v>
+        <v>0.008189</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.393374</v>
+        <v>0.021105</v>
       </c>
     </row>
     <row r="89">
@@ -4537,17 +4545,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miscellaneous income</t>
+          <t>Change in fair value of warrant derivative liability (Note 10)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
-        <v>0.000225</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.510968</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.393374</v>
       </c>
     </row>
     <row r="90">
@@ -4563,19 +4569,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TOTAL OTHER INCOME (EXPENSES)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Miscellaneous income</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>-0.513924</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>0.427708</v>
+        <v>0.000225</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -4591,19 +4595,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES</t>
+          <t>TOTAL OTHER INCOME (EXPENSES)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>-3.515948</v>
+        <v>-0.513924</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-3.93326</v>
+        <v>0.427708</v>
       </c>
     </row>
     <row r="92">
@@ -4619,19 +4623,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>INCOME TAX EXPENSE (Note 11)</t>
+          <t>LOSS BEFORE INCOME TAXES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.003718</v>
+        <v>-3.515948</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.005309</v>
+        <v>-3.93326</v>
       </c>
     </row>
     <row r="93">
@@ -4647,19 +4651,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NET AND COMPREHENSIVE LOSS $</t>
+          <t>INCOME TAX EXPENSE (Note 11)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>-3.519666</v>
+        <v>0.003718</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-3.938569</v>
+        <v>0.005309</v>
       </c>
     </row>
     <row r="94">
@@ -4675,15 +4679,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BASIC AND DILUTED NET LOSS PER COMMON SHARE $</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>NET AND COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E94" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-3.519666</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-3.938569</v>
       </c>
     </row>
     <row r="95">
@@ -4699,18 +4707,42 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
+          <t>BASIC AND DILUTED NET LOSS PER COMMON SHARE $</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>OTHER INCOME (EXPENSES)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>BASIC AND DILUTED WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E96" s="5" t="n">
         <v>210.615345</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F96" s="5" t="n">
         <v>235.88673</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/SVB.xlsx
+++ b/output/pdf_financials_xlsx/SVB.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004065</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.028443</v>
       </c>
     </row>
     <row r="13">
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.515948</v>
+        <v>-3.520013</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.93326</v>
+        <v>-3.961703</v>
       </c>
     </row>
     <row r="28">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.515948</v>
+        <v>-3.520013</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.93326</v>
+        <v>-3.961703</v>
       </c>
     </row>
     <row r="30">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">

--- a/output/pdf_financials_xlsx/SVB.xlsx
+++ b/output/pdf_financials_xlsx/SVB.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.571064</v>
+        <v>0.7975370000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.446853</v>
+        <v>0.647926</v>
       </c>
     </row>
     <row r="8">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.571064</v>
+        <v>0.7975370000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.446853</v>
+        <v>0.647926</v>
       </c>
     </row>
     <row r="11">
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019836</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.057224</v>
       </c>
     </row>
     <row r="112">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019836</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.057224</v>
       </c>
     </row>
     <row r="135">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.647377</v>
+        <v>-2.667213</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-4.209129</v>
+        <v>-4.266353</v>
       </c>
     </row>
   </sheetData>
@@ -3298,7 +3298,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.019836</v>
       </c>
@@ -4342,7 +4346,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>0.226473</v>
       </c>
